--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.43483</v>
+        <v>17.3409</v>
       </c>
       <c r="D2" t="n">
-        <v>17.22199</v>
+        <v>16.93763</v>
       </c>
       <c r="E2" t="n">
-        <v>17.14689</v>
+        <v>17.0215</v>
       </c>
       <c r="F2" t="n">
-        <v>43.75741</v>
+        <v>43.61182</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05092</v>
+        <v>0.05249</v>
       </c>
       <c r="H2" t="n">
-        <v>1.89757</v>
+        <v>1.88754</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.93881</v>
+        <v>17.67427</v>
       </c>
       <c r="D3" t="n">
-        <v>17.01626</v>
+        <v>17.24732</v>
       </c>
       <c r="E3" t="n">
-        <v>17.31413</v>
+        <v>17.25208</v>
       </c>
       <c r="F3" t="n">
-        <v>43.88367</v>
+        <v>44.82484</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05266</v>
+        <v>0.05128</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86556</v>
+        <v>1.88544</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.3543</v>
+        <v>17.1595</v>
       </c>
       <c r="D4" t="n">
-        <v>16.80067</v>
+        <v>16.86827</v>
       </c>
       <c r="E4" t="n">
-        <v>17.08285</v>
+        <v>17.14932</v>
       </c>
       <c r="F4" t="n">
-        <v>44.17503</v>
+        <v>43.19069</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05192</v>
+        <v>0.05195</v>
       </c>
       <c r="H4" t="n">
-        <v>1.91237</v>
+        <v>1.8426</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.17687</v>
+        <v>17.17007</v>
       </c>
       <c r="D6" t="n">
-        <v>16.32616</v>
+        <v>16.6214</v>
       </c>
       <c r="E6" t="n">
-        <v>16.584</v>
+        <v>17.06045</v>
       </c>
       <c r="F6" t="n">
-        <v>22.37197</v>
+        <v>22.33736</v>
       </c>
       <c r="G6" t="n">
-        <v>35.0067</v>
+        <v>35.2167</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.09849</v>
+        <v>17.22997</v>
       </c>
       <c r="D7" t="n">
-        <v>16.14142</v>
+        <v>16.23985</v>
       </c>
       <c r="E7" t="n">
-        <v>16.99987</v>
+        <v>16.75577</v>
       </c>
       <c r="F7" t="n">
-        <v>22.625</v>
+        <v>22.68416</v>
       </c>
       <c r="G7" t="n">
-        <v>34.78833</v>
+        <v>35.21779</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.9985</v>
+        <v>17.39379</v>
       </c>
       <c r="D8" t="n">
-        <v>16.38778</v>
+        <v>16.39478</v>
       </c>
       <c r="E8" t="n">
-        <v>16.92069</v>
+        <v>16.9774</v>
       </c>
       <c r="F8" t="n">
-        <v>22.58057</v>
+        <v>22.569</v>
       </c>
       <c r="G8" t="n">
-        <v>34.7501</v>
+        <v>35.46987</v>
       </c>
     </row>
   </sheetData>
